--- a/data/trans_orig/IP16A06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Clase-trans_orig.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>34668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33217</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70439</t>
+          <t>70364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75878</t>
+          <t>75875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>38701</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103989</t>
+          <t>103819</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109137</t>
+          <t>109136</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128496</t>
+          <t>129191</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134601</t>
+          <t>134648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235500</t>
+          <t>235482</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243026</t>
+          <t>242987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>21379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>46412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57412</t>
+          <t>56667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>69022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128397</t>
+          <t>128509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33947</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>31051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67379</t>
+          <t>66711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170765</t>
+          <t>171380</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177448</t>
+          <t>177461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>172916</t>
+          <t>172866</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>178245</t>
+          <t>178287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>345834</t>
+          <t>346248</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354565</t>
+          <t>354560</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>36704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96573</t>
+          <t>96181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>516</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31857</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26539</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61202</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65505</t>
+          <t>65507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152671</t>
+          <t>152502</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135374</t>
+          <t>135449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139812</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>290034</t>
+          <t>290372</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>295884</t>
+          <t>295656</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3309</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3599</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>18,53%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2619</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17215</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14419</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17215</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14548</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,88%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3247</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10456</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8397</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,12%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>70,65%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>48</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4328</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4282</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4619</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4133</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38064</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34461</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>36296</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33403</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33066</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38064</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34656</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,34%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70364</t>
+          <t>70996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75875</t>
+          <t>75879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1293</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3921</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4606</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4051</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22606</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19850</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22606</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19978</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38701</t>
+          <t>38146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5915</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5341</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2661</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6106</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>132636</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>128372</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>134574</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>107691</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>103819</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>109136</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>104393</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>109140</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,14%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>132636</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>129191</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>134648</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235482</t>
+          <t>235556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>242987</t>
+          <t>243027</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3362,102 +3362,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3652</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>798</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3970</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3574</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5345</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -3470,74 +3470,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24231</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21301</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26005</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22762</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22833</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>85,19%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24231</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21379</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>85,68%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>71</t>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46412</t>
+          <t>46472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3813,47 +3813,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>25619</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15961</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4391,102 +4391,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3731</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1366</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72062</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69452</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>59802</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>56667</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>57089</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72062</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>69022</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>187</t>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128509</t>
+          <t>128493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4734,102 +4734,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3240</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3175</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,74%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2579</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3930</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4518</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30584</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>36942</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34358</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>34423</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,26%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>33023</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>31051</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>98</t>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>67299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5077,102 +5077,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4280</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>6,94%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>39,49%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>36,29%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1465</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2817</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4770</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5017</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -5185,74 +5185,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13829</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11773</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>81,32%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>10977</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7137</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>7515</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>93,06%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>60,51%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>63,71%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>13829</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>11659</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>80,54%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>36</t>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21254</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5420,67 +5420,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6874</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>7501</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>176269</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>172421</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>178284</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>175307</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>171380</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>177461</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>170753</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>177569</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,35%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>176269</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>172866</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>178287</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>346248</t>
+          <t>346108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354560</t>
+          <t>354529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,107 +5992,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2717</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2906</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3323</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20382</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18311</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20382</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18122</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36704</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20130</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6796,42 +6796,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>11883</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6909,52 +6909,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11883</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,107 +7021,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3377</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42409</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39989</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>42409</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>39997</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96181</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3607</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3210</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -7477,74 +7477,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29619</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27340</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>34638</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>32172</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32383</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>90,51%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29619</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>27035</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>89,39%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>92</t>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61699</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65507</t>
+          <t>65517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5578</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3875</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3731</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4945</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -8163,74 +8163,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>138535</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>134816</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>139808</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>155236</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>152502</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>152646</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>138535</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>135449</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>139811</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>435</t>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>290372</t>
+          <t>289537</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>295656</t>
+          <t>295626</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
